--- a/resources/item/item.xlsx
+++ b/resources/item/item.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具表说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemType" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemBase" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chest" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potion" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidencePlantAccelerate" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gem" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameplayAbilityChoicePool" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fabao" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FabaoAbilityChoicePool" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="道具表说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ItemType" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ItemBase" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chest" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Potion" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ResidencePlantAccelerate" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Equipment" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gem" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="GameplayAbilityChoicePool" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fabao" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="FabaoAbilityChoicePool" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -1593,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="15.75" customWidth="1" style="23" min="1" max="3"/>
@@ -4175,30 +4175,460 @@
       <c r="L79" s="30" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="n"/>
+      <c r="A80" s="10" t="n">
+        <v>120033</v>
+      </c>
       <c r="B80" s="10" t="n"/>
       <c r="C80" s="10" t="n"/>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="n"/>
+      <c r="D80" s="10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>(PhyAtkCon,100,200)</t>
+        </is>
+      </c>
       <c r="H80" s="28" t="n"/>
       <c r="I80" s="28" t="n"/>
       <c r="J80" s="28" t="n"/>
       <c r="K80" s="30" t="n"/>
       <c r="L80" s="30" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>120034</v>
+      </c>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>(MagAtkCon,100,200)</t>
+        </is>
+      </c>
+      <c r="H81" s="28" t="n"/>
+      <c r="I81" s="28" t="n"/>
+      <c r="J81" s="28" t="n"/>
+      <c r="K81" s="30" t="n"/>
+      <c r="L81" s="30" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>120035</v>
+      </c>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>(CritCon,5,15)</t>
+        </is>
+      </c>
+      <c r="H82" s="28" t="n"/>
+      <c r="I82" s="28" t="n"/>
+      <c r="J82" s="28" t="n"/>
+      <c r="K82" s="30" t="n"/>
+      <c r="L82" s="30" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>120036</v>
+      </c>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="32" t="inlineStr">
+        <is>
+          <t>(StamCon,1,50)</t>
+        </is>
+      </c>
+      <c r="H83" s="28" t="n"/>
+      <c r="I83" s="28" t="n"/>
+      <c r="J83" s="28" t="n"/>
+      <c r="K83" s="30" t="n"/>
+      <c r="L83" s="30" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>120037</v>
+      </c>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="32" t="inlineStr">
+        <is>
+          <t>(ManaCon,1,50)</t>
+        </is>
+      </c>
+      <c r="H84" s="28" t="n"/>
+      <c r="I84" s="28" t="n"/>
+      <c r="J84" s="28" t="n"/>
+      <c r="K84" s="30" t="n"/>
+      <c r="L84" s="30" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>120038</v>
+      </c>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="32" t="inlineStr">
+        <is>
+          <t>PhyAtkCon,100,200</t>
+        </is>
+      </c>
+      <c r="H85" s="28" t="n"/>
+      <c r="I85" s="28" t="n"/>
+      <c r="J85" s="28" t="n"/>
+      <c r="K85" s="30" t="n"/>
+      <c r="L85" s="30" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>120039</v>
+      </c>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="32" t="inlineStr">
+        <is>
+          <t>MagAtkCon,100,200</t>
+        </is>
+      </c>
+      <c r="H86" s="28" t="n"/>
+      <c r="I86" s="28" t="n"/>
+      <c r="J86" s="28" t="n"/>
+      <c r="K86" s="30" t="n"/>
+      <c r="L86" s="30" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>120040</v>
+      </c>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="32" t="inlineStr">
+        <is>
+          <t>CritCon,5,15</t>
+        </is>
+      </c>
+      <c r="H87" s="28" t="n"/>
+      <c r="I87" s="28" t="n"/>
+      <c r="J87" s="28" t="n"/>
+      <c r="K87" s="30" t="n"/>
+      <c r="L87" s="30" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>120041</v>
+      </c>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n">
+        <v>200002</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="32" t="n"/>
+      <c r="H88" s="28" t="n"/>
+      <c r="I88" s="28" t="n"/>
+      <c r="J88" s="28" t="n"/>
+      <c r="K88" s="30" t="n"/>
+      <c r="L88" s="30" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>120042</v>
+      </c>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="10" t="n">
+        <v>200002</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="32" t="n"/>
+      <c r="H89" s="28" t="n"/>
+      <c r="I89" s="28" t="n"/>
+      <c r="J89" s="28" t="n"/>
+      <c r="K89" s="30" t="n"/>
+      <c r="L89" s="30" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>120043</v>
+      </c>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n">
+        <v>200002</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="32" t="n"/>
+      <c r="H90" s="28" t="n"/>
+      <c r="I90" s="28" t="n"/>
+      <c r="J90" s="28" t="n"/>
+      <c r="K90" s="30" t="n"/>
+      <c r="L90" s="30" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>120044</v>
+      </c>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="10" t="n">
+        <v>200003</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" s="32" t="inlineStr">
+        <is>
+          <t>(PhyAtkCon,100,200)</t>
+        </is>
+      </c>
+      <c r="H91" s="28" t="n"/>
+      <c r="I91" s="28" t="n"/>
+      <c r="J91" s="28" t="n"/>
+      <c r="K91" s="30" t="n"/>
+      <c r="L91" s="30" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>120045</v>
+      </c>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n">
+        <v>200003</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="32" t="inlineStr">
+        <is>
+          <t>(MagAtkCon,100,200)</t>
+        </is>
+      </c>
+      <c r="H92" s="28" t="n"/>
+      <c r="I92" s="28" t="n"/>
+      <c r="J92" s="28" t="n"/>
+      <c r="K92" s="30" t="n"/>
+      <c r="L92" s="30" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>120046</v>
+      </c>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="10" t="n">
+        <v>200003</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="32" t="inlineStr">
+        <is>
+          <t>(CritCon,5,15)</t>
+        </is>
+      </c>
+      <c r="H93" s="28" t="n"/>
+      <c r="I93" s="28" t="n"/>
+      <c r="J93" s="28" t="n"/>
+      <c r="K93" s="30" t="n"/>
+      <c r="L93" s="30" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>120047</v>
+      </c>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="10" t="n">
+        <v>200004</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" s="32" t="inlineStr">
+        <is>
+          <t>{'key': 'PhyAtkCon', 'min': 100, 'max': 200}</t>
+        </is>
+      </c>
+      <c r="H94" s="28" t="n"/>
+      <c r="I94" s="28" t="n"/>
+      <c r="J94" s="28" t="n"/>
+      <c r="K94" s="30" t="n"/>
+      <c r="L94" s="30" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>120048</v>
+      </c>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n">
+        <v>200004</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" s="32" t="inlineStr">
+        <is>
+          <t>{'key': 'MagAtkCon', 'min': 100, 'max': 200}</t>
+        </is>
+      </c>
+      <c r="H95" s="28" t="n"/>
+      <c r="I95" s="28" t="n"/>
+      <c r="J95" s="28" t="n"/>
+      <c r="K95" s="30" t="n"/>
+      <c r="L95" s="30" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>120049</v>
+      </c>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="10" t="n">
+        <v>200004</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="32" t="inlineStr">
+        <is>
+          <t>{'key': 'CritCon', 'min': 5, 'max': 15}</t>
+        </is>
+      </c>
+      <c r="H96" s="28" t="n"/>
+      <c r="I96" s="28" t="n"/>
+      <c r="J96" s="28" t="n"/>
+      <c r="K96" s="30" t="n"/>
+      <c r="L96" s="30" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="G97" s="32" t="n"/>
+      <c r="H97" s="28" t="n"/>
+      <c r="I97" s="28" t="n"/>
+      <c r="J97" s="28" t="n"/>
+      <c r="K97" s="30" t="n"/>
+      <c r="L97" s="30" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H49">
@@ -6662,7 +7092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V860"/>
+  <dimension ref="A1:V871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="12.75" customWidth="1" style="23" min="1" max="1"/>
@@ -43565,19 +43995,17 @@
       <c r="M858" s="23" t="n"/>
     </row>
     <row r="859">
-      <c r="A859" s="10" t="n"/>
-      <c r="B859" s="10" t="n"/>
+      <c r="A859" s="10" t="n">
+        <v>28529</v>
+      </c>
+      <c r="B859" s="10" t="inlineStr">
+        <is>
+          <t>麒麟蛋</t>
+        </is>
+      </c>
       <c r="C859" s="10" t="n"/>
-      <c r="D859" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="E859" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
+      <c r="D859" s="10" t="n"/>
+      <c r="E859" s="10" t="n"/>
       <c r="F859" s="10" t="n"/>
       <c r="G859" s="75" t="n"/>
       <c r="H859" s="10" t="n"/>
@@ -43588,19 +44016,310 @@
       <c r="M859" s="9" t="n"/>
     </row>
     <row r="860">
-      <c r="A860" s="10" t="n"/>
+      <c r="A860" s="10" t="n">
+        <v>29001</v>
+      </c>
       <c r="B860" s="10" t="n"/>
       <c r="C860" s="10" t="n"/>
-      <c r="D860" s="9" t="n"/>
+      <c r="D860" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="E860" s="10" t="n"/>
       <c r="F860" s="10" t="n"/>
       <c r="G860" s="75" t="n"/>
-      <c r="H860" s="10" t="n"/>
-      <c r="I860" s="10" t="n"/>
-      <c r="J860" s="10" t="n"/>
+      <c r="H860" s="10" t="inlineStr">
+        <is>
+          <t>Icon_qilin_egg</t>
+        </is>
+      </c>
+      <c r="I860" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J860" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="K860" s="10" t="n"/>
       <c r="L860" s="10" t="n"/>
       <c r="M860" s="9" t="n"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="10" t="n">
+        <v>29002</v>
+      </c>
+      <c r="B861" s="10" t="inlineStr">
+        <is>
+          <t>冰魄碎片</t>
+        </is>
+      </c>
+      <c r="C861" s="10" t="n"/>
+      <c r="D861" s="10" t="n"/>
+      <c r="E861" s="10" t="n"/>
+      <c r="F861" s="10" t="n"/>
+      <c r="G861" s="75" t="n"/>
+      <c r="H861" s="10" t="n"/>
+      <c r="I861" s="10" t="n"/>
+      <c r="J861" s="10" t="n"/>
+      <c r="K861" s="10" t="n"/>
+      <c r="L861" s="10" t="n"/>
+      <c r="M861" s="9" t="n"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="10" t="n">
+        <v>29003</v>
+      </c>
+      <c r="B862" s="10" t="inlineStr">
+        <is>
+          <t>冰魄之戒</t>
+        </is>
+      </c>
+      <c r="C862" s="10" t="n"/>
+      <c r="D862" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E862" s="10" t="n"/>
+      <c r="F862" s="10" t="n"/>
+      <c r="G862" s="75" t="n"/>
+      <c r="H862" s="10" t="inlineStr">
+        <is>
+          <t>Icon_ice_ring</t>
+        </is>
+      </c>
+      <c r="I862" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J862" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K862" s="10" t="n"/>
+      <c r="L862" s="10" t="n"/>
+      <c r="M862" s="9" t="n"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="10" t="n">
+        <v>29004</v>
+      </c>
+      <c r="B863" s="10" t="inlineStr">
+        <is>
+          <t>冰魄碎片</t>
+        </is>
+      </c>
+      <c r="C863" s="10" t="n"/>
+      <c r="D863" s="10" t="n"/>
+      <c r="E863" s="10" t="n"/>
+      <c r="F863" s="10" t="n"/>
+      <c r="G863" s="75" t="n"/>
+      <c r="H863" s="10" t="n"/>
+      <c r="I863" s="10" t="n"/>
+      <c r="J863" s="10" t="n"/>
+      <c r="K863" s="10" t="n"/>
+      <c r="L863" s="10" t="n"/>
+      <c r="M863" s="9" t="n"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="10" t="n">
+        <v>29005</v>
+      </c>
+      <c r="B864" s="10" t="inlineStr">
+        <is>
+          <t>冰魄之戒</t>
+        </is>
+      </c>
+      <c r="C864" s="10" t="n"/>
+      <c r="D864" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E864" s="10" t="n"/>
+      <c r="F864" s="10" t="n"/>
+      <c r="G864" s="75" t="n"/>
+      <c r="H864" s="10" t="inlineStr">
+        <is>
+          <t>Icon_ice_ring</t>
+        </is>
+      </c>
+      <c r="I864" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J864" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K864" s="10" t="n"/>
+      <c r="L864" s="10" t="n"/>
+      <c r="M864" s="9" t="n"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="10" t="n">
+        <v>29006</v>
+      </c>
+      <c r="B865" s="10" t="n"/>
+      <c r="C865" s="10" t="n"/>
+      <c r="D865" s="10" t="n"/>
+      <c r="E865" s="10" t="n"/>
+      <c r="F865" s="10" t="n"/>
+      <c r="G865" s="75" t="n"/>
+      <c r="H865" s="10" t="n"/>
+      <c r="I865" s="10" t="n"/>
+      <c r="J865" s="10" t="n"/>
+      <c r="K865" s="10" t="n"/>
+      <c r="L865" s="10" t="n"/>
+      <c r="M865" s="9" t="n"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="10" t="n">
+        <v>29007</v>
+      </c>
+      <c r="B866" s="10" t="inlineStr">
+        <is>
+          <t>灵泉图纸</t>
+        </is>
+      </c>
+      <c r="C866" s="10" t="n"/>
+      <c r="D866" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E866" s="10" t="n"/>
+      <c r="F866" s="10" t="n"/>
+      <c r="G866" s="75" t="n"/>
+      <c r="H866" s="10" t="inlineStr">
+        <is>
+          <t>Icon_lingquan_blueprint</t>
+        </is>
+      </c>
+      <c r="I866" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="J866" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K866" s="10" t="n"/>
+      <c r="L866" s="10" t="n"/>
+      <c r="M866" s="9" t="n"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="10" t="n">
+        <v>29008</v>
+      </c>
+      <c r="B867" s="10" t="n"/>
+      <c r="C867" s="10" t="n"/>
+      <c r="D867" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E867" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F867" s="10" t="n"/>
+      <c r="G867" s="75" t="n"/>
+      <c r="H867" s="10" t="inlineStr">
+        <is>
+          <t>Icon_potion_jiuzhuan</t>
+        </is>
+      </c>
+      <c r="I867" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J867" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K867" s="10" t="n"/>
+      <c r="L867" s="10" t="n"/>
+      <c r="M867" s="9" t="n"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="10" t="n">
+        <v>29009</v>
+      </c>
+      <c r="B868" s="10" t="n"/>
+      <c r="C868" s="10" t="n"/>
+      <c r="D868" s="10" t="n"/>
+      <c r="E868" s="10" t="n"/>
+      <c r="F868" s="10" t="n"/>
+      <c r="G868" s="75" t="n"/>
+      <c r="H868" s="10" t="n"/>
+      <c r="I868" s="10" t="n"/>
+      <c r="J868" s="10" t="n"/>
+      <c r="K868" s="10" t="n"/>
+      <c r="L868" s="10" t="n"/>
+      <c r="M868" s="9" t="n"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="10" t="n">
+        <v>29010</v>
+      </c>
+      <c r="B869" s="10" t="n"/>
+      <c r="C869" s="10" t="n"/>
+      <c r="D869" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E869" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F869" s="10" t="n"/>
+      <c r="G869" s="75" t="n"/>
+      <c r="H869" s="10" t="inlineStr">
+        <is>
+          <t>Icon_ice_piece</t>
+        </is>
+      </c>
+      <c r="I869" s="10" t="n">
+        <v>999</v>
+      </c>
+      <c r="J869" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K869" s="10" t="n"/>
+      <c r="L869" s="10" t="n"/>
+      <c r="M869" s="9" t="n"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="10" t="n">
+        <v>29011</v>
+      </c>
+      <c r="B870" s="10" t="n"/>
+      <c r="C870" s="10" t="n"/>
+      <c r="D870" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E870" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F870" s="10" t="n"/>
+      <c r="G870" s="75" t="n"/>
+      <c r="H870" s="10" t="inlineStr">
+        <is>
+          <t>Icon_ice_ring</t>
+        </is>
+      </c>
+      <c r="I870" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J870" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K870" s="10" t="n"/>
+      <c r="L870" s="10" t="n"/>
+      <c r="M870" s="9" t="n"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="10" t="n"/>
+      <c r="B871" s="10" t="n"/>
+      <c r="C871" s="10" t="n"/>
+      <c r="D871" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="E871" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="F871" s="10" t="n"/>
+      <c r="G871" s="75" t="n"/>
+      <c r="H871" s="10" t="n"/>
+      <c r="I871" s="10" t="n"/>
+      <c r="J871" s="10" t="n"/>
+      <c r="K871" s="10" t="n"/>
+      <c r="L871" s="10" t="n"/>
+      <c r="M871" s="9" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q771:Q779">

--- a/resources/item/item.xlsx
+++ b/resources/item/item.xlsx
@@ -1593,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="15.75" customWidth="1" style="23" min="1" max="3"/>
@@ -1725,33 +1725,25 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="n">
-        <v>100001</v>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>炼器装备属性</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
-        <is>
-          <t>全部位</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="n">
-        <v>1001</v>
-      </c>
-      <c r="E3" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>StamCon, 1, 10</t>
-        </is>
-      </c>
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="n"/>
       <c r="H3" s="28" t="n"/>
       <c r="I3" s="28" t="n"/>
       <c r="J3" s="28" t="n"/>
@@ -1759,33 +1751,13 @@
       <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="n">
-        <v>100002</v>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>炼器装备属性</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>全部位</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="n">
-        <v>1001</v>
-      </c>
-      <c r="E4" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>ManaCon, 1, 10</t>
-        </is>
-      </c>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="32" t="n"/>
       <c r="H4" s="28" t="n"/>
       <c r="I4" s="28" t="n"/>
       <c r="J4" s="28" t="n"/>
@@ -1794,7 +1766,7 @@
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="23" t="n">
-        <v>100003</v>
+        <v>100001</v>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -1817,13 +1789,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>StrengthCon, 1, 10</t>
+          <t>StamCon, 1, 10</t>
         </is>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="23" t="n">
-        <v>100004</v>
+        <v>100002</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -1846,13 +1818,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EndurCon, 1, 10</t>
+          <t>ManaCon, 1, 10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="23" t="n">
-        <v>100005</v>
+        <v>100003</v>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -1875,13 +1847,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AgilityCon, 4, 16</t>
+          <t>StrengthCon, 1, 10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="23" t="n">
-        <v>100006</v>
+        <v>100004</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -1904,13 +1876,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>WorldAttackCon, 2, 8</t>
+          <t>EndurCon, 1, 10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="23" t="n">
-        <v>100007</v>
+        <v>100005</v>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -1933,13 +1905,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>WorldMagicCon, 2, 8</t>
+          <t>AgilityCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="23" t="n">
-        <v>100008</v>
+        <v>100006</v>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -1962,13 +1934,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>WorldAttackDefCon, 2, 8</t>
+          <t>WorldAttackCon, 2, 8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="23" t="n">
-        <v>100009</v>
+        <v>100007</v>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -1991,13 +1963,13 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>WorldMagicDefCon, 2, 8</t>
+          <t>WorldMagicCon, 2, 8</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="23" t="n">
-        <v>100010</v>
+        <v>100008</v>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -2020,13 +1992,13 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>WorldSpeedCon, 1, 5</t>
+          <t>WorldAttackDefCon, 2, 8</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="23" t="n">
-        <v>100011</v>
+        <v>100009</v>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -2049,13 +2021,13 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>WorldHealCon, 10, 20</t>
+          <t>WorldMagicDefCon, 2, 8</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="23" t="n">
-        <v>100012</v>
+        <v>100010</v>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -2078,13 +2050,13 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HPMaxCon, 10, 25</t>
+          <t>WorldSpeedCon, 1, 5</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="23" t="n">
-        <v>100013</v>
+        <v>100011</v>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -2107,17 +2079,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MPMaxCon, 10, 30</t>
+          <t>WorldHealCon, 10, 20</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="23" t="n">
-        <v>100014</v>
+        <v>100012</v>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>筑基装备属性</t>
+          <t>炼器装备属性</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -2126,7 +2098,7 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>20</v>
@@ -2136,17 +2108,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>StamCon, 4, 16</t>
+          <t>HPMaxCon, 10, 25</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="23" t="n">
-        <v>100015</v>
+        <v>100013</v>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>筑基装备属性</t>
+          <t>炼器装备属性</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -2155,7 +2127,7 @@
         </is>
       </c>
       <c r="D17" s="23" t="n">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>20</v>
@@ -2165,13 +2137,13 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ManaCon, 4,16</t>
+          <t>MPMaxCon, 10, 30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="23" t="n">
-        <v>100016</v>
+        <v>100014</v>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
@@ -2194,13 +2166,13 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>StrengthCon, 4, 16</t>
+          <t>StamCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="23" t="n">
-        <v>100017</v>
+        <v>100015</v>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
@@ -2223,13 +2195,13 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>EndurCon, 4, 16</t>
+          <t>ManaCon, 4,16</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="23" t="n">
-        <v>100018</v>
+        <v>100016</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
@@ -2252,17 +2224,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AgilityCon, 4, 16</t>
+          <t>StrengthCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="23" t="n">
-        <v>100019</v>
+        <v>100017</v>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>炼器装备属性</t>
+          <t>筑基装备属性</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -2271,7 +2243,7 @@
         </is>
       </c>
       <c r="D21" s="23" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>20</v>
@@ -2281,17 +2253,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>WorldAttackCon, 5, 13</t>
+          <t>EndurCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="23" t="n">
-        <v>100020</v>
+        <v>100018</v>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>炼器装备属性</t>
+          <t>筑基装备属性</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -2300,7 +2272,7 @@
         </is>
       </c>
       <c r="D22" s="23" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>20</v>
@@ -2310,13 +2282,13 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>WorldMagicCon, 5, 13</t>
+          <t>AgilityCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="23" t="n">
-        <v>100021</v>
+        <v>100019</v>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
@@ -2339,13 +2311,13 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>WorldAttackDefCon, 4, 12</t>
+          <t>WorldAttackCon, 5, 13</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="23" t="n">
-        <v>100022</v>
+        <v>100020</v>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
@@ -2368,13 +2340,13 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>WorldMagicDefCon, 4, 12</t>
+          <t>WorldMagicCon, 5, 13</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="23" t="n">
-        <v>100023</v>
+        <v>100021</v>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
@@ -2397,13 +2369,13 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>WorldSpeedCon, 3, 7</t>
+          <t>WorldAttackDefCon, 4, 12</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="23" t="n">
-        <v>100024</v>
+        <v>100022</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
@@ -2426,13 +2398,13 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>WorldHealCon, 20, 45</t>
+          <t>WorldMagicDefCon, 4, 12</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="23" t="n">
-        <v>100025</v>
+        <v>100023</v>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
@@ -2455,13 +2427,13 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HPMaxCon, 18, 40</t>
+          <t>WorldSpeedCon, 3, 7</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="23" t="n">
-        <v>100026</v>
+        <v>100024</v>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
@@ -2484,17 +2456,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MPMaxCon, 20, 50</t>
+          <t>WorldHealCon, 20, 45</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="23" t="n">
-        <v>110001</v>
+        <v>100025</v>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>特技</t>
+          <t>炼器装备属性</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -2503,33 +2475,27 @@
         </is>
       </c>
       <c r="D29" s="23" t="n">
-        <v>1101</v>
+        <v>1001</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>20</v>
       </c>
       <c r="F29" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>100023</v>
-      </c>
-      <c r="I29" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>damage,100,150</t>
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HPMaxCon, 18, 40</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="23" t="n">
-        <v>110002</v>
+        <v>100026</v>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>特技</t>
+          <t>炼器装备属性</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -2538,29 +2504,23 @@
         </is>
       </c>
       <c r="D30" s="23" t="n">
-        <v>1101</v>
+        <v>1001</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>20</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <v>100024</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>damage,100,150</t>
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MPMaxCon, 20, 50</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="23" t="n">
-        <v>110003</v>
+        <v>110001</v>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
@@ -2582,7 +2542,7 @@
         <v>2</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>100025</v>
+        <v>100023</v>
       </c>
       <c r="I31" s="23" t="n">
         <v>1</v>
@@ -2595,7 +2555,7 @@
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="23" t="n">
-        <v>110004</v>
+        <v>110002</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
@@ -2617,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>100026</v>
+        <v>100024</v>
       </c>
       <c r="I32" s="23" t="n">
         <v>1</v>
@@ -2630,7 +2590,7 @@
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="23" t="n">
-        <v>110005</v>
+        <v>110003</v>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
@@ -2652,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>100027</v>
+        <v>100025</v>
       </c>
       <c r="I33" s="23" t="n">
         <v>1</v>
@@ -2665,7 +2625,7 @@
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="23" t="n">
-        <v>110006</v>
+        <v>110004</v>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
@@ -2687,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>100028</v>
+        <v>100026</v>
       </c>
       <c r="I34" s="23" t="n">
         <v>1</v>
@@ -2700,7 +2660,7 @@
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="23" t="n">
-        <v>110007</v>
+        <v>110005</v>
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
@@ -2722,7 +2682,7 @@
         <v>2</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>100029</v>
+        <v>100027</v>
       </c>
       <c r="I35" s="23" t="n">
         <v>1</v>
@@ -2735,7 +2695,7 @@
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="23" t="n">
-        <v>110008</v>
+        <v>110006</v>
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
@@ -2757,7 +2717,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>100030</v>
+        <v>100028</v>
       </c>
       <c r="I36" s="23" t="n">
         <v>1</v>
@@ -2770,7 +2730,7 @@
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="23" t="n">
-        <v>110009</v>
+        <v>110007</v>
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
@@ -2792,7 +2752,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>100031</v>
+        <v>100029</v>
       </c>
       <c r="I37" s="23" t="n">
         <v>1</v>
@@ -2805,7 +2765,7 @@
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="23" t="n">
-        <v>110010</v>
+        <v>110008</v>
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
@@ -2827,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>100032</v>
+        <v>100030</v>
       </c>
       <c r="I38" s="23" t="n">
         <v>1</v>
@@ -2840,7 +2800,7 @@
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="23" t="n">
-        <v>110011</v>
+        <v>110009</v>
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
@@ -2862,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>100033</v>
+        <v>100031</v>
       </c>
       <c r="I39" s="23" t="n">
         <v>1</v>
@@ -2875,7 +2835,7 @@
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="23" t="n">
-        <v>110012</v>
+        <v>110010</v>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
@@ -2897,7 +2857,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>100034</v>
+        <v>100032</v>
       </c>
       <c r="I40" s="23" t="n">
         <v>1</v>
@@ -2910,7 +2870,7 @@
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="23" t="n">
-        <v>110013</v>
+        <v>110011</v>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
@@ -2932,7 +2892,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>100035</v>
+        <v>100033</v>
       </c>
       <c r="I41" s="23" t="n">
         <v>1</v>
@@ -2945,7 +2905,7 @@
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="23" t="n">
-        <v>110014</v>
+        <v>110012</v>
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
@@ -2967,7 +2927,7 @@
         <v>2</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>100036</v>
+        <v>100034</v>
       </c>
       <c r="I42" s="23" t="n">
         <v>1</v>
@@ -2980,7 +2940,7 @@
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="23" t="n">
-        <v>110015</v>
+        <v>110013</v>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
@@ -3002,7 +2962,7 @@
         <v>2</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>100037</v>
+        <v>100035</v>
       </c>
       <c r="I43" s="23" t="n">
         <v>1</v>
@@ -3015,7 +2975,7 @@
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="23" t="n">
-        <v>110016</v>
+        <v>110014</v>
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
@@ -3037,7 +2997,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>100038</v>
+        <v>100036</v>
       </c>
       <c r="I44" s="23" t="n">
         <v>1</v>
@@ -3050,7 +3010,7 @@
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="23" t="n">
-        <v>110017</v>
+        <v>110015</v>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
@@ -3072,7 +3032,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>100039</v>
+        <v>100037</v>
       </c>
       <c r="I45" s="23" t="n">
         <v>1</v>
@@ -3085,7 +3045,7 @@
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="23" t="n">
-        <v>110018</v>
+        <v>110016</v>
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
@@ -3107,7 +3067,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>100040</v>
+        <v>100038</v>
       </c>
       <c r="I46" s="23" t="n">
         <v>1</v>
@@ -3120,7 +3080,7 @@
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="23" t="n">
-        <v>110019</v>
+        <v>110017</v>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
@@ -3141,8 +3101,8 @@
       <c r="F47" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="54" t="n">
-        <v>100041</v>
+      <c r="H47" s="23" t="n">
+        <v>100039</v>
       </c>
       <c r="I47" s="23" t="n">
         <v>1</v>
@@ -3155,11 +3115,11 @@
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="23" t="n">
-        <v>120001</v>
+        <v>110018</v>
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>特技</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
@@ -3168,33 +3128,33 @@
         </is>
       </c>
       <c r="D48" s="23" t="n">
-        <v>1201</v>
+        <v>1101</v>
       </c>
       <c r="E48" s="23" t="n">
         <v>20</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="23" t="n"/>
-      <c r="I48" s="23" t="n"/>
-      <c r="J48" s="19" t="n"/>
-      <c r="K48" s="54" t="n">
-        <v>100001</v>
-      </c>
-      <c r="L48" s="19" t="inlineStr">
-        <is>
-          <t>rate,1,3</t>
+        <v>2</v>
+      </c>
+      <c r="H48" s="23" t="n">
+        <v>100040</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>damage,100,150</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="23" t="n">
-        <v>120002</v>
+        <v>110019</v>
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>特技</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
@@ -3203,29 +3163,29 @@
         </is>
       </c>
       <c r="D49" s="23" t="n">
-        <v>1201</v>
+        <v>1101</v>
       </c>
       <c r="E49" s="23" t="n">
         <v>20</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="54" t="n"/>
-      <c r="I49" s="23" t="n"/>
-      <c r="J49" s="19" t="n"/>
-      <c r="K49" s="54" t="n">
-        <v>100002</v>
-      </c>
-      <c r="L49" s="19" t="inlineStr">
-        <is>
-          <t>rate,1,3</t>
+        <v>2</v>
+      </c>
+      <c r="H49" s="54" t="n">
+        <v>100041</v>
+      </c>
+      <c r="I49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>damage,100,150</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="23" t="n">
-        <v>120003</v>
+        <v>120001</v>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
@@ -3247,7 +3207,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="54" t="n">
-        <v>100003</v>
+        <v>100001</v>
       </c>
       <c r="L50" s="19" t="inlineStr">
         <is>
@@ -3257,7 +3217,7 @@
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="23" t="n">
-        <v>120004</v>
+        <v>120002</v>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
@@ -3279,7 +3239,7 @@
         <v>3</v>
       </c>
       <c r="K51" s="54" t="n">
-        <v>100004</v>
+        <v>100002</v>
       </c>
       <c r="L51" s="19" t="inlineStr">
         <is>
@@ -3289,7 +3249,7 @@
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="23" t="n">
-        <v>120005</v>
+        <v>120003</v>
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
@@ -3311,17 +3271,17 @@
         <v>3</v>
       </c>
       <c r="K52" s="54" t="n">
-        <v>100005</v>
+        <v>100003</v>
       </c>
       <c r="L52" s="19" t="inlineStr">
         <is>
-          <t>seal,5,10</t>
+          <t>rate,1,3</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="23" t="n">
-        <v>120006</v>
+        <v>120004</v>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
@@ -3343,17 +3303,17 @@
         <v>3</v>
       </c>
       <c r="K53" s="54" t="n">
-        <v>100006</v>
+        <v>100004</v>
       </c>
       <c r="L53" s="19" t="inlineStr">
         <is>
-          <t>seal,5,10</t>
+          <t>rate,1,3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="23" t="n">
-        <v>120007</v>
+        <v>120005</v>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
@@ -3375,17 +3335,17 @@
         <v>3</v>
       </c>
       <c r="K54" s="54" t="n">
-        <v>100007</v>
+        <v>100005</v>
       </c>
       <c r="L54" s="19" t="inlineStr">
         <is>
-          <t>rate,1,3</t>
+          <t>seal,5,10</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="23" t="n">
-        <v>120008</v>
+        <v>120006</v>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
@@ -3407,17 +3367,17 @@
         <v>3</v>
       </c>
       <c r="K55" s="54" t="n">
-        <v>100008</v>
+        <v>100006</v>
       </c>
       <c r="L55" s="19" t="inlineStr">
         <is>
-          <t>rate,1,3</t>
+          <t>seal,5,10</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="23" t="n">
-        <v>120009</v>
+        <v>120007</v>
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
@@ -3439,7 +3399,7 @@
         <v>3</v>
       </c>
       <c r="K56" s="54" t="n">
-        <v>100009</v>
+        <v>100007</v>
       </c>
       <c r="L56" s="19" t="inlineStr">
         <is>
@@ -3449,7 +3409,7 @@
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="23" t="n">
-        <v>120010</v>
+        <v>120008</v>
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
@@ -3471,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="K57" s="54" t="n">
-        <v>100010</v>
+        <v>100008</v>
       </c>
       <c r="L57" s="19" t="inlineStr">
         <is>
@@ -3481,7 +3441,7 @@
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="23" t="n">
-        <v>120011</v>
+        <v>120009</v>
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
@@ -3503,7 +3463,7 @@
         <v>3</v>
       </c>
       <c r="K58" s="54" t="n">
-        <v>100011</v>
+        <v>100009</v>
       </c>
       <c r="L58" s="19" t="inlineStr">
         <is>
@@ -3513,7 +3473,7 @@
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="23" t="n">
-        <v>120012</v>
+        <v>120010</v>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
@@ -3535,7 +3495,7 @@
         <v>3</v>
       </c>
       <c r="K59" s="54" t="n">
-        <v>100012</v>
+        <v>100010</v>
       </c>
       <c r="L59" s="19" t="inlineStr">
         <is>
@@ -3545,7 +3505,7 @@
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="23" t="n">
-        <v>120013</v>
+        <v>120011</v>
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
@@ -3567,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="K60" s="54" t="n">
-        <v>100013</v>
+        <v>100011</v>
       </c>
       <c r="L60" s="19" t="inlineStr">
         <is>
@@ -3577,7 +3537,7 @@
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="23" t="n">
-        <v>120014</v>
+        <v>120012</v>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
@@ -3599,7 +3559,7 @@
         <v>3</v>
       </c>
       <c r="K61" s="54" t="n">
-        <v>100014</v>
+        <v>100012</v>
       </c>
       <c r="L61" s="19" t="inlineStr">
         <is>
@@ -3609,7 +3569,7 @@
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="23" t="n">
-        <v>120015</v>
+        <v>120013</v>
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
@@ -3631,7 +3591,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="54" t="n">
-        <v>100015</v>
+        <v>100013</v>
       </c>
       <c r="L62" s="19" t="inlineStr">
         <is>
@@ -3641,7 +3601,7 @@
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="23" t="n">
-        <v>120016</v>
+        <v>120014</v>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
@@ -3663,7 +3623,7 @@
         <v>3</v>
       </c>
       <c r="K63" s="54" t="n">
-        <v>100016</v>
+        <v>100014</v>
       </c>
       <c r="L63" s="19" t="inlineStr">
         <is>
@@ -3673,7 +3633,7 @@
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="23" t="n">
-        <v>120017</v>
+        <v>120015</v>
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
@@ -3695,7 +3655,7 @@
         <v>3</v>
       </c>
       <c r="K64" s="54" t="n">
-        <v>100017</v>
+        <v>100015</v>
       </c>
       <c r="L64" s="19" t="inlineStr">
         <is>
@@ -3705,7 +3665,7 @@
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="23" t="n">
-        <v>120018</v>
+        <v>120016</v>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
@@ -3727,7 +3687,7 @@
         <v>3</v>
       </c>
       <c r="K65" s="54" t="n">
-        <v>100018</v>
+        <v>100016</v>
       </c>
       <c r="L65" s="19" t="inlineStr">
         <is>
@@ -3737,7 +3697,7 @@
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="23" t="n">
-        <v>120019</v>
+        <v>120017</v>
       </c>
       <c r="B66" s="23" t="inlineStr">
         <is>
@@ -3759,17 +3719,17 @@
         <v>3</v>
       </c>
       <c r="K66" s="54" t="n">
-        <v>100019</v>
+        <v>100017</v>
       </c>
       <c r="L66" s="19" t="inlineStr">
         <is>
-          <t>seal,5,10</t>
+          <t>rate,1,3</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="23" t="n">
-        <v>120020</v>
+        <v>120018</v>
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
@@ -3791,17 +3751,17 @@
         <v>3</v>
       </c>
       <c r="K67" s="54" t="n">
-        <v>100020</v>
+        <v>100018</v>
       </c>
       <c r="L67" s="19" t="inlineStr">
         <is>
-          <t>seal,5,10</t>
+          <t>rate,1,3</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="23" t="n">
-        <v>120021</v>
+        <v>120019</v>
       </c>
       <c r="B68" s="23" t="inlineStr">
         <is>
@@ -3823,17 +3783,17 @@
         <v>3</v>
       </c>
       <c r="K68" s="54" t="n">
-        <v>100021</v>
+        <v>100019</v>
       </c>
       <c r="L68" s="19" t="inlineStr">
         <is>
-          <t>rate,1,3</t>
+          <t>seal,5,10</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="23" t="n">
-        <v>120022</v>
+        <v>120020</v>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
@@ -3855,17 +3815,17 @@
         <v>3</v>
       </c>
       <c r="K69" s="54" t="n">
-        <v>100022</v>
+        <v>100020</v>
       </c>
       <c r="L69" s="19" t="inlineStr">
         <is>
-          <t>rate,1,3</t>
+          <t>seal,5,10</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="23" t="n">
-        <v>120023</v>
+        <v>120021</v>
       </c>
       <c r="B70" s="23" t="inlineStr">
         <is>
@@ -3887,7 +3847,7 @@
         <v>3</v>
       </c>
       <c r="K70" s="54" t="n">
-        <v>100023</v>
+        <v>100021</v>
       </c>
       <c r="L70" s="19" t="inlineStr">
         <is>
@@ -3897,7 +3857,7 @@
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="23" t="n">
-        <v>120024</v>
+        <v>120022</v>
       </c>
       <c r="B71" s="23" t="inlineStr">
         <is>
@@ -3919,7 +3879,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="54" t="n">
-        <v>100024</v>
+        <v>100022</v>
       </c>
       <c r="L71" s="19" t="inlineStr">
         <is>
@@ -3929,7 +3889,7 @@
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="23" t="n">
-        <v>120025</v>
+        <v>120023</v>
       </c>
       <c r="B72" s="23" t="inlineStr">
         <is>
@@ -3951,7 +3911,7 @@
         <v>3</v>
       </c>
       <c r="K72" s="54" t="n">
-        <v>100025</v>
+        <v>100023</v>
       </c>
       <c r="L72" s="19" t="inlineStr">
         <is>
@@ -3961,7 +3921,7 @@
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="23" t="n">
-        <v>120026</v>
+        <v>120024</v>
       </c>
       <c r="B73" s="23" t="inlineStr">
         <is>
@@ -3983,7 +3943,7 @@
         <v>3</v>
       </c>
       <c r="K73" s="54" t="n">
-        <v>100026</v>
+        <v>100024</v>
       </c>
       <c r="L73" s="19" t="inlineStr">
         <is>
@@ -3993,7 +3953,7 @@
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="23" t="n">
-        <v>120027</v>
+        <v>120025</v>
       </c>
       <c r="B74" s="23" t="inlineStr">
         <is>
@@ -4015,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="K74" s="54" t="n">
-        <v>100027</v>
+        <v>100025</v>
       </c>
       <c r="L74" s="19" t="inlineStr">
         <is>
@@ -4025,7 +3985,7 @@
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="23" t="n">
-        <v>120028</v>
+        <v>120026</v>
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
@@ -4047,7 +4007,7 @@
         <v>3</v>
       </c>
       <c r="K75" s="54" t="n">
-        <v>100028</v>
+        <v>100026</v>
       </c>
       <c r="L75" s="19" t="inlineStr">
         <is>
@@ -4057,57 +4017,67 @@
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="23" t="n">
-        <v>200008</v>
-      </c>
-      <c r="B76" s="23" t="n"/>
-      <c r="C76" s="23" t="n"/>
-      <c r="D76" s="23" t="n"/>
+        <v>120027</v>
+      </c>
+      <c r="B76" s="23" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>全部位</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>1201</v>
+      </c>
       <c r="E76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="23" t="n"/>
-      <c r="K76" s="54" t="n"/>
-      <c r="L76" s="19" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F76" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" s="54" t="n">
+        <v>100027</v>
+      </c>
+      <c r="L76" s="19" t="inlineStr">
+        <is>
+          <t>rate,1,3</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="10" t="n"/>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="n"/>
-      <c r="H77" s="28" t="n"/>
-      <c r="I77" s="28" t="n"/>
-      <c r="J77" s="28" t="n"/>
-      <c r="K77" s="30" t="n"/>
-      <c r="L77" s="30" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="n"/>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="32" t="n"/>
-      <c r="H78" s="28" t="n"/>
-      <c r="I78" s="28" t="n"/>
-      <c r="J78" s="28" t="n"/>
-      <c r="K78" s="30" t="n"/>
-      <c r="L78" s="30" t="n"/>
+      <c r="A77" s="23" t="n">
+        <v>120028</v>
+      </c>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>全部位</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>1201</v>
+      </c>
+      <c r="E77" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F77" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" s="54" t="n">
+        <v>100028</v>
+      </c>
+      <c r="L77" s="19" t="inlineStr">
+        <is>
+          <t>rate,1,3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H49">
@@ -5326,7 +5296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="14.75" customWidth="1" min="1" max="1"/>
@@ -5398,60 +5368,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="n">
-        <v>200001</v>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>附加属性-物理攻击</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="n">
-        <v>200001</v>
-      </c>
-      <c r="D3" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>WorldAttackCon, 10, 20</t>
-        </is>
-      </c>
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="n">
-        <v>200002</v>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>附加属性-法术攻击</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="n">
-        <v>200001</v>
-      </c>
-      <c r="D4" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>WorldMagicCon, 10, 30</t>
-        </is>
-      </c>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="32" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="23" t="n">
-        <v>200003</v>
+        <v>200001</v>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>附加属性-治疗强度</t>
+          <t>附加属性-物理攻击</t>
         </is>
       </c>
       <c r="C5" s="23" t="n">
@@ -5465,17 +5415,17 @@
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>WorldHealCon, 4, 16</t>
+          <t>WorldAttackCon, 10, 20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n">
-        <v>200004</v>
+        <v>200002</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>附加属性-物理防御</t>
+          <t>附加属性-法术攻击</t>
         </is>
       </c>
       <c r="C6" s="23" t="n">
@@ -5489,17 +5439,17 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>WorldAttackDefCon, 4,16</t>
+          <t>WorldMagicCon, 10, 30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="n">
-        <v>200005</v>
+        <v>200003</v>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>附加属性-法术防御</t>
+          <t>附加属性-治疗强度</t>
         </is>
       </c>
       <c r="C7" s="23" t="n">
@@ -5513,17 +5463,17 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>WorldMagicDefCon, 4, 16</t>
+          <t>WorldHealCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="n">
-        <v>200006</v>
+        <v>200004</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>附加属性-封印抵抗</t>
+          <t>附加属性-物理防御</t>
         </is>
       </c>
       <c r="C8" s="23" t="n">
@@ -5537,17 +5487,17 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>WorldSealResCon, 4, 16</t>
+          <t>WorldAttackDefCon, 4,16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="n">
-        <v>200007</v>
+        <v>200005</v>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>附加属性-速度</t>
+          <t>附加属性-法术防御</t>
         </is>
       </c>
       <c r="C9" s="23" t="n">
@@ -5561,59 +5511,66 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>WorldSpeedCon,4,16</t>
+          <t>WorldMagicDefCon, 4, 16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="n">
-        <v>200008</v>
-      </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
+        <v>200006</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>附加属性-封印抵抗</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>200001</v>
+      </c>
       <c r="D10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>WorldSealResCon, 4, 16</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="n"/>
+      <c r="A11" s="23" t="n">
+        <v>200007</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>附加属性-速度</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>200001</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>WorldSpeedCon,4,16</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="32" t="n"/>
+      <c r="A12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n"/>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -6220,7 +6177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="15.25" customWidth="1" style="23" min="1" max="1"/>
@@ -6562,13 +6519,6 @@
       <c r="C19" s="49" t="inlineStr">
         <is>
           <t>28500, 29999</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>称为“DAOJULEIXING_TEST”,同时增加道具名称为"DAOJU_TEST"</t>
         </is>
       </c>
     </row>
@@ -43515,9 +43465,7 @@
       <c r="D859" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E859" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="E859" s="10" t="n"/>
       <c r="F859" s="10" t="n"/>
       <c r="G859" s="75" t="inlineStr">
         <is>
@@ -43532,9 +43480,7 @@
       <c r="I859" s="10" t="n">
         <v>999</v>
       </c>
-      <c r="J859" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="J859" s="10" t="n"/>
       <c r="K859" s="10" t="n"/>
       <c r="L859" s="10" t="n"/>
       <c r="M859" s="9" t="n"/>
@@ -43581,7 +43527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="17.33203125" customWidth="1" style="23" min="1" max="1"/>
@@ -43815,15 +43761,6 @@
           <t>万物生礼包</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>这个戒指在 item.xlsx 的 Chest sheet 作宝箱绑定到首通奖励包。</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="52" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6 B8:B12">
